--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487047_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487047_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6015</v>
+        <v>5.5317</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8437</v>
+        <v>5.4431</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7578</v>
+        <v>0.0885</v>
       </c>
       <c r="G2" t="n">
         <v>1.7216</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5011</v>
+        <v>0.4313</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2049</v>
+        <v>-0.1956</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2961</v>
+        <v>0.6269</v>
       </c>
       <c r="V2" t="n">
         <v>2.4137</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0191</v>
+        <v>1.4767</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3398</v>
+        <v>1.7758</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3588</v>
+        <v>-0.2991</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3498</v>
+        <v>1.141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3498</v>
+        <v>-0.2213</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.3624</v>
       </c>
       <c r="J3" t="n">
-        <v>1.424</v>
+        <v>4.2776</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3919</v>
+        <v>1.7956</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0321</v>
+        <v>2.482</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0742</v>
+        <v>-3.1365</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.042</v>
+        <v>-2.0169</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0321</v>
+        <v>-1.1196</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.0881</v>
+        <v>-0.193</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.2112</v>
+        <v>-2.3161</v>
       </c>
       <c r="R3" t="n">
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6452</v>
+        <v>-0.0853</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9915</v>
+        <v>-0.4293</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.344</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1122</v>
+        <v>0.614</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4559</v>
+        <v>0.2436</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6562</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2671</v>
+        <v>0.9235</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0748</v>
+        <v>-1.1409</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8077</v>
+        <v>2.0644</v>
       </c>
       <c r="G4" t="n">
-        <v>1.141</v>
+        <v>0.3498</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2213</v>
+        <v>0.3498</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3624</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2776</v>
+        <v>1.424</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7956</v>
+        <v>1.3919</v>
       </c>
       <c r="L4" t="n">
-        <v>2.482</v>
+        <v>0.0321</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.1365</v>
+        <v>-1.0742</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0169</v>
+        <v>-1.042</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1196</v>
+        <v>-0.0321</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.193</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3161</v>
+        <v>-5.2112</v>
       </c>
       <c r="R4" t="n">
         <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2949</v>
+        <v>0.5496</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1303</v>
+        <v>0.1904</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1646</v>
+        <v>0.3592</v>
       </c>
       <c r="V4" t="n">
-        <v>0.614</v>
+        <v>3.1122</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2436</v>
+        <v>2.4559</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3704</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1989</v>
+        <v>-0.0988</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1821</v>
+        <v>-0.0819</v>
       </c>
       <c r="F5" t="n">
         <v>-0.0169</v>
@@ -844,10 +844,10 @@
         <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1785</v>
+        <v>0.2786</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U5" t="n">
         <v>0.2974</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.207</v>
+        <v>-1.0999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4121</v>
+        <v>-2.1566</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7948</v>
+        <v>1.0568</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3695</v>
+        <v>1.4463</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8807</v>
+        <v>1.4448</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5112</v>
+        <v>0.0014</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6719000000000001</v>
+        <v>2.5741</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>2.6804</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6512</v>
+        <v>-0.1064</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0414</v>
+        <v>-1.1278</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9014</v>
+        <v>-1.2356</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.14</v>
+        <v>0.1078</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.772</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>-5.0182</v>
       </c>
       <c r="R6" t="n">
-        <v>0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0654</v>
+        <v>-0.2228</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.119</v>
+        <v>-0.2842</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0535</v>
+        <v>0.0614</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2605</v>
+        <v>-1.1267</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1566</v>
+        <v>-0.4121</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8961</v>
+        <v>-0.7145</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4463</v>
+        <v>-0.3695</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4448</v>
+        <v>-0.8807</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0014</v>
+        <v>0.5112</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5741</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6804</v>
+        <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1064</v>
+        <v>0.6512</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1278</v>
+        <v>-1.0414</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2356</v>
+        <v>-0.9014</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1078</v>
+        <v>-0.14</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8951</v>
+        <v>-0.772</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0182</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3834</v>
+        <v>0.0149</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2842</v>
+        <v>-0.119</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0992</v>
+        <v>0.1338</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.615</v>
+        <v>-1.9154</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2588</v>
+        <v>-0.5593</v>
       </c>
       <c r="F8" t="n">
         <v>-1.3561</v>
@@ -1078,10 +1078,10 @@
         <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4455</v>
+        <v>0.1451</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2512</v>
+        <v>-0.0492</v>
       </c>
       <c r="U8" t="n">
         <v>0.1943</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3025</v>
+        <v>-3.3898</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4933</v>
+        <v>-2.3931</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8093</v>
+        <v>-0.9967</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2879</v>
@@ -1156,13 +1156,13 @@
         <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5294</v>
+        <v>0.4422</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7674</v>
+        <v>0.58</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.655</v>
+        <v>-4.6526</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.938</v>
+        <v>-3.3372</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.717</v>
+        <v>-1.3155</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6049</v>
@@ -1234,13 +1234,13 @@
         <v>2.3161</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3663</v>
+        <v>-0.3639</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1303</v>
+        <v>-0.5294</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.236</v>
+        <v>0.1656</v>
       </c>
       <c r="V10" t="n">
         <v>-1.842</v>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.351200000000002</v>
+        <v>-4.3513</v>
       </c>
       <c r="E11" t="n">
         <v>-2.862200000000001</v>
@@ -1315,7 +1315,7 @@
         <v>1.1897</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5732</v>
+        <v>-1.5729</v>
       </c>
       <c r="U11" t="n">
         <v>2.7626</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5128</v>
+        <v>5.2613</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5472</v>
+        <v>3.9478</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9656</v>
+        <v>1.3136</v>
       </c>
       <c r="G12" t="n">
         <v>3.2607</v>
@@ -1390,13 +1390,13 @@
         <v>2.8951</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9868</v>
+        <v>-0.2383</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9518</v>
+        <v>-0.5512</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.035</v>
+        <v>0.313</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6562</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7172</v>
+        <v>4.3716</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0859</v>
+        <v>3.6867</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6313</v>
+        <v>0.6848</v>
       </c>
       <c r="G13" t="n">
         <v>2.4004</v>
@@ -1468,13 +1468,13 @@
         <v>3.6672</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1224</v>
+        <v>-0.468</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2492</v>
+        <v>-0.6484</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1269</v>
+        <v>0.1804</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>P. OSES TOME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3477</v>
+        <v>1.9995</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1079</v>
+        <v>2.7165</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2398</v>
+        <v>-0.7169</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6304</v>
+        <v>1.6104</v>
       </c>
       <c r="H14" t="n">
-        <v>2.342</v>
+        <v>-0.1283</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2885</v>
+        <v>1.7386</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4107</v>
+        <v>3.0116</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2236</v>
+        <v>1.1073</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1871</v>
+        <v>1.9043</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7803</v>
+        <v>-1.4013</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8817</v>
+        <v>-1.2356</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1014</v>
+        <v>-0.1657</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8951</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9526</v>
+        <v>-0.4528</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5996</v>
+        <v>-0.4699</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3529</v>
+        <v>0.0172</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2702</v>
+        <v>1.228</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0422</v>
+        <v>3.0699</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.228</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. OSES TOME</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1845</v>
+        <v>0.8922</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1156</v>
+        <v>-0.294</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9311</v>
+        <v>1.1863</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6104</v>
+        <v>2.6304</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1283</v>
+        <v>2.342</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7386</v>
+        <v>0.2885</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0116</v>
+        <v>3.4107</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1073</v>
+        <v>3.2236</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9043</v>
+        <v>0.1871</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4013</v>
+        <v>-0.7803</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2356</v>
+        <v>-0.8817</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1657</v>
+        <v>0.1014</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>2.8951</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2678</v>
+        <v>0.4971</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0708</v>
+        <v>0.1977</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.197</v>
+        <v>0.2994</v>
       </c>
       <c r="V15" t="n">
-        <v>1.228</v>
+        <v>-1.2702</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0699</v>
+        <v>-0.0422</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.842</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.555</v>
+        <v>0.1405</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0728</v>
+        <v>-2.2731</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6278</v>
+        <v>2.4137</v>
       </c>
       <c r="G16" t="n">
         <v>-2.357</v>
@@ -1702,13 +1702,13 @@
         <v>2.7021</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4957</v>
+        <v>0.0813</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0132</v>
+        <v>-0.187</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4825</v>
+        <v>0.2683</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2859</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0857</v>
+        <v>-0.0321</v>
       </c>
       <c r="E17" t="n">
         <v>-1.4224</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3367</v>
+        <v>1.3902</v>
       </c>
       <c r="G17" t="n">
         <v>0.8984</v>
@@ -1780,13 +1780,13 @@
         <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2313</v>
+        <v>-0.1778</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U17" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="V17" t="n">
         <v>0.9843</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6576</v>
+        <v>-0.3969</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5624</v>
+        <v>-0.4018</v>
       </c>
       <c r="G18" t="n">
         <v>-0.968</v>
@@ -1858,13 +1858,13 @@
         <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7548</v>
+        <v>-0.4941</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5949</v>
+        <v>-0.4947</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.16</v>
+        <v>0.0007</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9792</v>
+        <v>-0.7522</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8028</v>
+        <v>-0.6025</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1765</v>
+        <v>-0.1497</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7852</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4871</v>
+        <v>-0.2601</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.238</v>
+        <v>-0.0377</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2492</v>
+        <v>-0.2224</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2859</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0608</v>
+        <v>-3.0142</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9989</v>
+        <v>-1.8987</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.062</v>
+        <v>-1.1155</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4127</v>
@@ -2014,13 +2014,13 @@
         <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0238</v>
+        <v>0.0704</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2617</v>
+        <v>0.2082</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1826</v>
+        <v>-4.1186</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9755</v>
+        <v>-2.3761</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2071</v>
+        <v>-1.7425</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0382</v>
@@ -2092,13 +2092,13 @@
         <v>3.2811</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1884</v>
+        <v>0.2525</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2644</v>
+        <v>-0.1361</v>
       </c>
       <c r="U21" t="n">
-        <v>0.924</v>
+        <v>0.3886</v>
       </c>
       <c r="V21" t="n">
         <v>-3.6839</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.351299999999999</v>
+        <v>4.3511</v>
       </c>
       <c r="E22" t="n">
-        <v>1.489</v>
+        <v>1.4892</v>
       </c>
       <c r="F22" t="n">
-        <v>2.862099999999999</v>
+        <v>2.862200000000001</v>
       </c>
       <c r="G22" t="n">
         <v>3.239199999999999</v>
@@ -2170,13 +2170,13 @@
         <v>21.2308</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1897</v>
+        <v>-1.1898</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.7629</v>
+        <v>-2.7625</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5729</v>
+        <v>1.573</v>
       </c>
       <c r="V22" t="n">
         <v>-6.383599999999999</v>
